--- a/data/nzd0164/nzd0164.xlsx
+++ b/data/nzd0164/nzd0164.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E344"/>
+  <dimension ref="A1:E348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7656,6 +7656,90 @@
         <v>333.98</v>
       </c>
       <c r="E344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>346.44</v>
+      </c>
+      <c r="C345" t="n">
+        <v>334.8</v>
+      </c>
+      <c r="D345" t="n">
+        <v>334.55</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>347.84</v>
+      </c>
+      <c r="C346" t="n">
+        <v>335.86</v>
+      </c>
+      <c r="D346" t="n">
+        <v>336</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>346.72</v>
+      </c>
+      <c r="C347" t="n">
+        <v>336.06</v>
+      </c>
+      <c r="D347" t="n">
+        <v>337.53</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>346.05</v>
+      </c>
+      <c r="C348" t="n">
+        <v>336.77</v>
+      </c>
+      <c r="D348" t="n">
+        <v>338.84</v>
+      </c>
+      <c r="E348" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -7672,7 +7756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B386"/>
+  <dimension ref="A1:B390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11535,6 +11619,46 @@
       </c>
       <c r="B386" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>
@@ -11703,28 +11827,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06614226575806692</v>
+        <v>-0.0563677697709792</v>
       </c>
       <c r="J2" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="K2" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0130050305814744</v>
+        <v>0.009612413841060041</v>
       </c>
       <c r="M2" t="n">
-        <v>3.385856592067536</v>
+        <v>3.395873518323981</v>
       </c>
       <c r="N2" t="n">
-        <v>18.17319292730396</v>
+        <v>18.17275509294926</v>
       </c>
       <c r="O2" t="n">
-        <v>4.263002806391753</v>
+        <v>4.262951453271461</v>
       </c>
       <c r="P2" t="n">
-        <v>344.252228287473</v>
+        <v>344.1468524885894</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11781,28 +11905,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1546572025327488</v>
+        <v>-0.1524106956080358</v>
       </c>
       <c r="J3" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="K3" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04944256564636884</v>
+        <v>0.04924312711054291</v>
       </c>
       <c r="M3" t="n">
-        <v>3.961389790673474</v>
+        <v>3.926032782618222</v>
       </c>
       <c r="N3" t="n">
-        <v>25.17023118357692</v>
+        <v>24.89665959944958</v>
       </c>
       <c r="O3" t="n">
-        <v>5.016994237945357</v>
+        <v>4.989655258577447</v>
       </c>
       <c r="P3" t="n">
-        <v>339.0381306428529</v>
+        <v>339.0138925333881</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11859,28 +11983,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04480892122866219</v>
+        <v>0.04631714476829155</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="K4" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001687989107408305</v>
+        <v>0.001849147822023611</v>
       </c>
       <c r="M4" t="n">
-        <v>6.175147797317902</v>
+        <v>6.120221573543167</v>
       </c>
       <c r="N4" t="n">
-        <v>64.99727856840066</v>
+        <v>64.28275067749051</v>
       </c>
       <c r="O4" t="n">
-        <v>8.062088970508864</v>
+        <v>8.017652441799315</v>
       </c>
       <c r="P4" t="n">
-        <v>334.8701611776107</v>
+        <v>334.8538590948989</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11918,7 +12042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E344"/>
+  <dimension ref="A1:E348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21209,6 +21333,114 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-36.757819563501045,175.75745786059625</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-36.75786513187323,175.7565127846831</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-36.758191240883804,175.75568212060293</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-36.757831880433805,175.75746122717734</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-36.75787410620358,175.75651683787154</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-36.75820281295172,175.75568964910806</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-36.75782202688761,175.75745853391237</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-36.75787579947343,175.7565176026242</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-36.758215023477916,175.75569759298156</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-36.75781613235546,175.75745692276314</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-36.75788181058139,175.75652031749638</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-36.758225478241656,175.75570439460083</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0164/nzd0164.xlsx
+++ b/data/nzd0164/nzd0164.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E348"/>
+  <dimension ref="A1:E350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7740,6 +7740,48 @@
         <v>338.84</v>
       </c>
       <c r="E348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>348.62</v>
+      </c>
+      <c r="C349" t="n">
+        <v>338.49</v>
+      </c>
+      <c r="D349" t="n">
+        <v>341.94</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>346.62</v>
+      </c>
+      <c r="C350" t="n">
+        <v>338.38</v>
+      </c>
+      <c r="D350" t="n">
+        <v>342.48</v>
+      </c>
+      <c r="E350" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -7756,7 +7798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B390"/>
+  <dimension ref="A1:B392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11659,6 +11701,26 @@
       </c>
       <c r="B390" t="n">
         <v>-0.32</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -11827,28 +11889,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0563677697709792</v>
+        <v>-0.05073739222500313</v>
       </c>
       <c r="J2" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K2" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009612413841060041</v>
+        <v>0.00783747614718755</v>
       </c>
       <c r="M2" t="n">
-        <v>3.395873518323981</v>
+        <v>3.404608509006774</v>
       </c>
       <c r="N2" t="n">
-        <v>18.17275509294926</v>
+        <v>18.21444221879846</v>
       </c>
       <c r="O2" t="n">
-        <v>4.262951453271461</v>
+        <v>4.267838120032021</v>
       </c>
       <c r="P2" t="n">
-        <v>344.1468524885894</v>
+        <v>344.0859412643709</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11905,28 +11967,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1524106956080358</v>
+        <v>-0.1484345037258214</v>
       </c>
       <c r="J3" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04924312711054291</v>
+        <v>0.0472636126851036</v>
       </c>
       <c r="M3" t="n">
-        <v>3.926032782618222</v>
+        <v>3.921321808610206</v>
       </c>
       <c r="N3" t="n">
-        <v>24.89665959944958</v>
+        <v>24.82381770263991</v>
       </c>
       <c r="O3" t="n">
-        <v>4.989655258577447</v>
+        <v>4.98235062020327</v>
       </c>
       <c r="P3" t="n">
-        <v>339.0138925333881</v>
+        <v>338.970865612326</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11983,28 +12045,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04631714476829155</v>
+        <v>0.05321658683000617</v>
       </c>
       <c r="J4" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K4" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001849147822023611</v>
+        <v>0.0024623484268812</v>
       </c>
       <c r="M4" t="n">
-        <v>6.120221573543167</v>
+        <v>6.117208430420255</v>
       </c>
       <c r="N4" t="n">
-        <v>64.28275067749051</v>
+        <v>64.12491904035952</v>
       </c>
       <c r="O4" t="n">
-        <v>8.017652441799315</v>
+        <v>8.007803633978515</v>
       </c>
       <c r="P4" t="n">
-        <v>334.8538590948989</v>
+        <v>334.7791933223974</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12042,7 +12104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E348"/>
+  <dimension ref="A1:E350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21441,6 +21503,60 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-36.75783874272485,175.7574631028445</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-36.75789637270167,175.75652689437175</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-36.75825021852034,175.7557204900433</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-36.75782114710669,175.7574582934423</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-36.75789544140329,175.75652647375756</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-36.758254528116986,175.75572329376666</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0164/nzd0164.xlsx
+++ b/data/nzd0164/nzd0164.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E350"/>
+  <dimension ref="A1:E351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7782,6 +7782,27 @@
         <v>342.48</v>
       </c>
       <c r="E350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>347.7</v>
+      </c>
+      <c r="C351" t="n">
+        <v>339.39</v>
+      </c>
+      <c r="D351" t="n">
+        <v>343.95</v>
+      </c>
+      <c r="E351" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -7798,7 +7819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B392"/>
+  <dimension ref="A1:B393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11721,6 +11742,16 @@
       </c>
       <c r="B392" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -11889,28 +11920,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05073739222500313</v>
+        <v>-0.04793213864743897</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00783747614718755</v>
+        <v>0.007017394043899672</v>
       </c>
       <c r="M2" t="n">
-        <v>3.404608509006774</v>
+        <v>3.408786278148491</v>
       </c>
       <c r="N2" t="n">
-        <v>18.21444221879846</v>
+        <v>18.23264863928601</v>
       </c>
       <c r="O2" t="n">
-        <v>4.267838120032021</v>
+        <v>4.269970566559682</v>
       </c>
       <c r="P2" t="n">
-        <v>344.0859412643709</v>
+        <v>344.0554861764706</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11967,28 +11998,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1484345037258214</v>
+        <v>-0.1459427342208647</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0472636126851036</v>
+        <v>0.0459382560384215</v>
       </c>
       <c r="M3" t="n">
-        <v>3.921321808610206</v>
+        <v>3.92118922947418</v>
       </c>
       <c r="N3" t="n">
-        <v>24.82381770263991</v>
+        <v>24.80831722738619</v>
       </c>
       <c r="O3" t="n">
-        <v>4.98235062020327</v>
+        <v>4.980794838917398</v>
       </c>
       <c r="P3" t="n">
-        <v>338.970865612326</v>
+        <v>338.9438138477697</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12045,28 +12076,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05321658683000617</v>
+        <v>0.05757316829641811</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0024623484268812</v>
+        <v>0.002891210676985945</v>
       </c>
       <c r="M4" t="n">
-        <v>6.117208430420255</v>
+        <v>6.120274732837228</v>
       </c>
       <c r="N4" t="n">
-        <v>64.12491904035952</v>
+        <v>64.1111307448941</v>
       </c>
       <c r="O4" t="n">
-        <v>8.007803633978515</v>
+        <v>8.006942659023736</v>
       </c>
       <c r="P4" t="n">
-        <v>334.7791933223974</v>
+        <v>334.7318963248761</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12104,7 +12135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E350"/>
+  <dimension ref="A1:E351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21557,6 +21588,33 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-36.75783064874054,175.75746089051918</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-36.75790399241558,175.75653033576108</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-36.75826625979636,175.75573092612626</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
